--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/6672-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/6672-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{52E96C31-F11D-481C-8575-27CAA3C61619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4AD14E4F-74E1-42FA-96AC-5644752CC68F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{DCF2AD36-2EFF-4024-B893-0E77EB2EA991}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{1DEA76FE-7177-42D2-B5F4-33C672ED2F13}"/>
   </bookViews>
   <sheets>
     <sheet name="6672-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1475,25 +1475,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D35E9446-75BA-4B75-9C07-8D9F81174AF2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C32F319-F044-458E-953D-4AAA4171913A}">
   <dimension ref="A1:R25"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="9.109375" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="11.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1521,7 +1521,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1551,7 +1551,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1597,7 +1597,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1647,7 +1647,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1701,7 +1701,7 @@
         <v>4.4800000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1757,7 +1757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1813,7 +1813,7 @@
         <v>4.4800000000000004</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="39">
         <v>2024</v>
       </c>
@@ -1867,7 +1867,7 @@
         <v>3.97</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
@@ -1923,7 +1923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>25</v>
       </c>
@@ -1979,7 +1979,7 @@
         <v>3.97</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="37">
         <v>2023</v>
       </c>
@@ -2033,7 +2033,7 @@
         <v>4.1500000000000004</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>25</v>
       </c>
@@ -2089,7 +2089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>25</v>
       </c>
@@ -2145,7 +2145,7 @@
         <v>4.1500000000000004</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="39">
         <v>2022</v>
       </c>
@@ -2199,7 +2199,7 @@
         <v>8.11</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>25</v>
       </c>
@@ -2255,7 +2255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>25</v>
       </c>
@@ -2311,7 +2311,7 @@
         <v>8.11</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="37">
         <v>2021</v>
       </c>
@@ -2365,7 +2365,7 @@
         <v>2.14</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
@@ -2421,7 +2421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -2477,7 +2477,7 @@
         <v>2.14</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="39">
         <v>2020</v>
       </c>
@@ -2531,7 +2531,7 @@
         <v>5.85</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>25</v>
       </c>
@@ -2587,7 +2587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>25</v>
       </c>
@@ -2643,7 +2643,7 @@
         <v>5.85</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="37">
         <v>2019</v>
       </c>
@@ -2697,7 +2697,7 @@
         <v>4.1500000000000004</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="39">
         <v>2018</v>
       </c>
@@ -2751,7 +2751,7 @@
         <v>1.57</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="37" t="s">
         <v>44</v>
       </c>
